--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.31691762868184</v>
+        <v>8.6639991146608</v>
       </c>
       <c r="D2" t="n">
-        <v>50.50745619511012</v>
+        <v>8.207461631705396</v>
       </c>
       <c r="E2" t="n">
-        <v>17.78442399554254</v>
+        <v>2.889968899275662</v>
       </c>
       <c r="F2" t="n">
-        <v>13.84132671996794</v>
+        <v>2.24921559199479</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.95580634777894</v>
+        <v>4.705318531514077</v>
       </c>
       <c r="D3" t="n">
-        <v>27.31815855484877</v>
+        <v>4.439200765162925</v>
       </c>
       <c r="E3" t="n">
-        <v>17.78442399554254</v>
+        <v>2.889968899275662</v>
       </c>
       <c r="F3" t="n">
-        <v>13.84132671996794</v>
+        <v>2.24921559199479</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.01702767840052</v>
+        <v>2.440266997740084</v>
       </c>
       <c r="D4" t="n">
-        <v>14.10566349081353</v>
+        <v>2.292170317257199</v>
       </c>
       <c r="E4" t="n">
-        <v>17.78442399554254</v>
+        <v>2.889968899275662</v>
       </c>
       <c r="F4" t="n">
-        <v>13.84132671996794</v>
+        <v>2.24921559199479</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.93828700637054</v>
+        <v>3.564971638535213</v>
       </c>
       <c r="D5" t="n">
-        <v>22.60310971296395</v>
+        <v>3.673005328356641</v>
       </c>
       <c r="E5" t="n">
-        <v>17.78442399554254</v>
+        <v>2.889968899275662</v>
       </c>
       <c r="F5" t="n">
-        <v>13.84132671996794</v>
+        <v>2.24921559199479</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>49.86231041578399</v>
+        <v>8.102625442564898</v>
       </c>
       <c r="D6" t="n">
-        <v>47.80292675238812</v>
+        <v>7.767975597263069</v>
       </c>
       <c r="E6" t="n">
-        <v>17.78442399554254</v>
+        <v>2.889968899275662</v>
       </c>
       <c r="F6" t="n">
-        <v>13.84132671996794</v>
+        <v>2.24921559199479</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.14600407480113</v>
+        <v>9.123725662155183</v>
       </c>
       <c r="D7" t="n">
-        <v>51.19419028950962</v>
+        <v>8.319055922045314</v>
       </c>
       <c r="E7" t="n">
-        <v>17.78442399554254</v>
+        <v>2.889968899275662</v>
       </c>
       <c r="F7" t="n">
-        <v>13.84132671996794</v>
+        <v>2.24921559199479</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>64.92175081520828</v>
+        <v>10.54978450747135</v>
       </c>
       <c r="D8" t="n">
-        <v>41.22596568806582</v>
+        <v>6.699219424310696</v>
       </c>
       <c r="E8" t="n">
-        <v>17.78442399554254</v>
+        <v>2.889968899275662</v>
       </c>
       <c r="F8" t="n">
-        <v>13.84132671996794</v>
+        <v>2.24921559199479</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
